--- a/product_selector_out/STM32MP1 series.xlsx
+++ b/product_selector_out/STM32MP1 series.xlsx
@@ -1744,7 +1744,7 @@
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp131a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="BC15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp131c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="BC18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp133a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="BC19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp133c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="BC22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp135a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="BC23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp135c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="BC26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp151a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="BC27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp151c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="BC30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp153a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="BC31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp153c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="BC34" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp157a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="BC35" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp157c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8658,9 +8658,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -8908,9 +8908,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8935,9 +8935,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -9185,9 +9185,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9766,9 +9766,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -10016,9 +10016,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10043,9 +10043,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -10293,9 +10293,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10874,9 +10874,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -11124,9 +11124,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11151,9 +11151,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -11401,9 +11401,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11982,9 +11982,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -12127,14 +12127,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AI26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AH26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AI26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AJ26" s="6" t="inlineStr">
@@ -12232,9 +12232,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12259,9 +12259,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -12404,14 +12404,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AI27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AH27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AI27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AJ27" s="6" t="inlineStr">
@@ -12509,9 +12509,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13090,9 +13090,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -13235,14 +13235,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AI30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AH30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AI30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AJ30" s="6" t="inlineStr">
@@ -13340,9 +13340,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13367,9 +13367,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -13512,14 +13512,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AI31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AH31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AI31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AJ31" s="6" t="inlineStr">
@@ -13617,9 +13617,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14198,9 +14198,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -14343,14 +14343,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AI34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AH34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AI34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AJ34" s="6" t="inlineStr">
@@ -14448,9 +14448,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14475,9 +14475,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -14620,14 +14620,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AI35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AH35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AI35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AJ35" s="6" t="inlineStr">
@@ -14725,9 +14725,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14746,7 +14746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14912,7 +14912,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32MP151D</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -14934,7 +14934,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32MP151D</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -14956,7 +14956,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32MP151D</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14978,7 +14978,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32MP151F</t>
+          <t>STM32MP153C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -15000,7 +15000,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32MP151F</t>
+          <t>STM32MP153C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -15022,7 +15022,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32MP151F</t>
+          <t>STM32MP153C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -15044,7 +15044,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP157A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -15066,7 +15066,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP157A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -15088,7 +15088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP157A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -15110,7 +15110,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP157C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -15132,7 +15132,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP157C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -15154,7 +15154,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP157C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -15168,402 +15168,6 @@
         </is>
       </c>
       <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32MP153D</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32MP153D</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32MP153D</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32MP153F</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32MP153F</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32MP153F</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32MP157A</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32MP157A</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32MP157A</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32MP157C</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32MP157C</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32MP157C</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32MP157D</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32MP157D</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32MP157D</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32MP157F</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32MP157F</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32MP157F</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
         <is>
           <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32MP1 series.xlsx
+++ b/product_selector_out/STM32MP1 series.xlsx
@@ -1744,7 +1744,7 @@
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp131a.pdf</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="BC15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp131c.pdf</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="BC18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp133a.pdf</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="BC19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp133c.pdf</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="BC22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp135a.pdf</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="BC23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp135c.pdf</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="BC26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp151a.pdf</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="BC27" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp151c.pdf</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="BC30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp153a.pdf</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="BC31" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp153c.pdf</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="BC34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp157a.pdf</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="BC35" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp157c.pdf</t>
         </is>
       </c>
     </row>
@@ -8658,9 +8658,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -8908,9 +8908,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8935,9 +8935,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -9185,9 +9185,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9766,9 +9766,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -10016,9 +10016,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10043,9 +10043,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -10293,9 +10293,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10874,9 +10874,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -11124,9 +11124,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11151,9 +11151,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -11401,9 +11401,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11982,9 +11982,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -12127,14 +12127,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AI26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AH26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AI26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AJ26" s="6" t="inlineStr">
@@ -12232,9 +12232,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12259,9 +12259,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -12404,14 +12404,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AI27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AH27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AI27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AJ27" s="6" t="inlineStr">
@@ -12509,9 +12509,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13090,9 +13090,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -13235,14 +13235,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AI30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AH30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AI30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AJ30" s="6" t="inlineStr">
@@ -13340,9 +13340,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC30" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13367,9 +13367,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -13512,14 +13512,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AI31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AH31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AI31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AJ31" s="6" t="inlineStr">
@@ -13617,9 +13617,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC31" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -14198,9 +14198,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -14343,14 +14343,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AI34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AH34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AI34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AJ34" s="6" t="inlineStr">
@@ -14448,9 +14448,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -14475,9 +14475,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -14620,14 +14620,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AH35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AI35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AH35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AI35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AJ35" s="6" t="inlineStr">
@@ -14725,9 +14725,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC35" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -14746,7 +14746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14912,7 +14912,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP151D</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -14934,7 +14934,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP151D</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -14956,7 +14956,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP151D</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14978,7 +14978,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP151F</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -15000,7 +15000,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP151F</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -15022,7 +15022,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP151F</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -15044,7 +15044,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32MP157A</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -15066,7 +15066,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32MP157A</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -15088,7 +15088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32MP157A</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -15110,7 +15110,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32MP157C</t>
+          <t>STM32MP153C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -15132,7 +15132,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32MP157C</t>
+          <t>STM32MP153C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -15154,20 +15154,416 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>STM32MP153C</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32MP153D</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32MP153D</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32MP153D</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32MP153F</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32MP153F</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32MP153F</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32MP157A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32MP157A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32MP157A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>STM32MP157C</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32MP157C</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32MP157C</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Timers (32-bit) typ</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32MP157D</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32MP157D</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32MP157D</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32MP157F</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32MP157F</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32MP157F</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32MP1 series.xlsx
+++ b/product_selector_out/STM32MP1 series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC35"/>
+  <dimension ref="A1:BD35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.828125" customWidth="1" min="1" max="1"/>
@@ -557,7 +557,8 @@
     <col width="18" customWidth="1" min="52" max="52"/>
     <col width="18" customWidth="1" min="53" max="53"/>
     <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="52" customWidth="1" min="55" max="55"/>
+    <col width="18" customWidth="1" min="55" max="55"/>
+    <col width="52" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -839,6 +840,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -916,6 +922,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1190,6 +1197,11 @@
       </c>
       <c r="BC12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp131a.pdf</t>
         </is>
       </c>
@@ -1467,6 +1479,11 @@
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp131c.pdf</t>
         </is>
       </c>
@@ -1747,6 +1764,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2024,6 +2046,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2298,6 +2325,11 @@
       </c>
       <c r="BC16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp133a.pdf</t>
         </is>
       </c>
@@ -2575,6 +2607,11 @@
       </c>
       <c r="BC17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp133c.pdf</t>
         </is>
       </c>
@@ -2855,6 +2892,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3132,6 +3174,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3406,6 +3453,11 @@
       </c>
       <c r="BC20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp135a.pdf</t>
         </is>
       </c>
@@ -3683,6 +3735,11 @@
       </c>
       <c r="BC21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp135c.pdf</t>
         </is>
       </c>
@@ -3963,6 +4020,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4240,6 +4302,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4514,6 +4581,11 @@
       </c>
       <c r="BC24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp151a.pdf</t>
         </is>
       </c>
@@ -4791,6 +4863,11 @@
       </c>
       <c r="BC25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp151c.pdf</t>
         </is>
       </c>
@@ -5071,6 +5148,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5348,6 +5430,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -5622,6 +5709,11 @@
       </c>
       <c r="BC28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp153a.pdf</t>
         </is>
       </c>
@@ -5899,6 +5991,11 @@
       </c>
       <c r="BC29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp153c.pdf</t>
         </is>
       </c>
@@ -6179,6 +6276,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD30" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -6456,6 +6558,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD31" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -6730,6 +6837,11 @@
       </c>
       <c r="BC32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp157a.pdf</t>
         </is>
       </c>
@@ -7007,6 +7119,11 @@
       </c>
       <c r="BC33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp157c.pdf</t>
         </is>
       </c>
@@ -7287,6 +7404,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD34" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -7564,9 +7686,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="56">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AU10:AU11"/>
@@ -7578,16 +7705,18 @@
     <mergeCell ref="AH10:AH11"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="M10:M11"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AJ10:AJ11"/>
-    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AP10:AP11"/>
-    <mergeCell ref="BA10:BA11"/>
-    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="AK10:AK11"/>
     <mergeCell ref="L10:L11"/>
@@ -7598,9 +7727,8 @@
     <mergeCell ref="Z10:Z11"/>
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
-    <mergeCell ref="A1:BC8"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A9:BC9"/>
+    <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="AC10:AD10"/>
     <mergeCell ref="AE10:AF10"/>
     <mergeCell ref="A10:A11"/>
@@ -7660,7 +7788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC35"/>
+  <dimension ref="A1:BD35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7718,6 +7846,7 @@
     <col width="16" customWidth="1" min="53" max="53"/>
     <col width="16" customWidth="1" min="54" max="54"/>
     <col width="16" customWidth="1" min="55" max="55"/>
+    <col width="16" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8005,6 +8134,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -8082,6 +8216,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8354,7 +8489,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="6" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8631,7 +8771,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="6" t="inlineStr">
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8913,6 +9058,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -9190,6 +9340,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -9462,7 +9617,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="6" t="inlineStr">
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9739,7 +9899,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="6" t="inlineStr">
+      <c r="BC17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10021,6 +10186,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -10298,6 +10468,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -10570,7 +10745,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="6" t="inlineStr">
+      <c r="BC20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10847,7 +11027,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC21" s="6" t="inlineStr">
+      <c r="BC21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11129,6 +11314,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -11406,6 +11596,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -11678,7 +11873,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC24" s="6" t="inlineStr">
+      <c r="BC24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11955,7 +12155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC25" s="6" t="inlineStr">
+      <c r="BC25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12237,6 +12442,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -12514,6 +12724,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -12786,7 +13001,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC28" s="6" t="inlineStr">
+      <c r="BC28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13063,7 +13283,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC29" s="6" t="inlineStr">
+      <c r="BC29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13345,6 +13570,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -13622,6 +13852,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -13894,7 +14129,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC32" s="6" t="inlineStr">
+      <c r="BC32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14171,7 +14411,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC33" s="6" t="inlineStr">
+      <c r="BC33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14453,6 +14698,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -14730,11 +14980,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BC9"/>
-    <mergeCell ref="A1:BC8"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
